--- a/class_diagram/controller/view/manager/成績管理sys_クラス図_controller_view_manager.xlsx
+++ b/class_diagram/controller/view/manager/成績管理sys_クラス図_controller_view_manager.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29607"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20357"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="337" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF4DFB4A-BCEF-48E8-8890-BB91A057971B}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\java_fri_sys\seiseki_manage_sys\class_diagram\controller\view\manager\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8350AB1-25A6-4527-B69B-A86CB26EC45D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="4" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MajorsGetViewController" sheetId="3" r:id="rId1"/>
@@ -26,10 +31,10 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -38,12 +43,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -612,7 +624,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>@GetMapping("/manager/major/register")</a:t>
+            <a:t>@GetMapping("/manager/major_register")</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2448,18 +2460,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FAD6FA3-7B26-471B-B3D8-8BC601EF4900}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData/>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63A8633E-387F-40CD-BD90-4057C77280B7}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData/>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2468,8 +2483,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8829FDBE-9BFC-4C0E-89F2-C13862F39AFB}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData/>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2478,8 +2494,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA2B0658-91AA-4EFF-842D-3941C1AF5682}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData/>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2488,8 +2505,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A4375CD-953A-4466-B799-B5CFC9858533}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData/>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2498,8 +2516,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23901DE6-5F7D-4F8C-96AD-8F2E5E915077}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData/>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2508,8 +2527,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B570C0A3-9704-4150-B1EB-E56BF2A1A796}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData/>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/class_diagram/controller/view/manager/成績管理sys_クラス図_controller_view_manager.xlsx
+++ b/class_diagram/controller/view/manager/成績管理sys_クラス図_controller_view_manager.xlsx
@@ -1,25 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20357"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29609"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\java_fri_sys\seiseki_manage_sys\class_diagram\controller\view\manager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8350AB1-25A6-4527-B69B-A86CB26EC45D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{C8350AB1-25A6-4527-B69B-A86CB26EC45D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFAC53B5-5635-4683-9743-7DBC6A9E978D}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="MajorsGetViewController" sheetId="3" r:id="rId1"/>
+    <sheet name="LoginViewController" sheetId="8" r:id="rId1"/>
     <sheet name="MajorRegisterViewController" sheetId="2" r:id="rId2"/>
     <sheet name="MajorSetViewController" sheetId="6" r:id="rId3"/>
-    <sheet name="MajorsSearchGetViewController" sheetId="7" r:id="rId4"/>
-    <sheet name="LoginViewController" sheetId="8" r:id="rId5"/>
+    <sheet name="MajorsGetViewController" sheetId="3" r:id="rId4"/>
+    <sheet name="MajorsSearchGetViewController" sheetId="7" r:id="rId5"/>
     <sheet name="MajorGetViewController" sheetId="4" r:id="rId6"/>
     <sheet name="Sheet1" sheetId="5" state="hidden" r:id="rId7"/>
+    <sheet name="SubjectRegisterViewController" sheetId="11" r:id="rId8"/>
+    <sheet name="SubjectSetViewController" sheetId="10" r:id="rId9"/>
+    <sheet name="SubjectsGetViewController" sheetId="12" r:id="rId10"/>
+    <sheet name="SubjectGetViewController" sheetId="9" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -31,10 +35,10 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -43,7 +47,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -103,22 +107,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
+      <xdr:colOff>342900</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="角丸四角形 2">
+        <xdr:cNvPr id="2" name="角丸四角形 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{822B201D-DF36-4DB1-A2CC-BF7C2A34D922}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A92F80CA-9A40-43A6-AC20-AAAD467F4BB0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -126,7 +130,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1028700"/>
+          <a:off x="695325" y="914400"/>
           <a:ext cx="12677775" cy="5495925"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
@@ -155,10 +159,101 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+        <a:bodyPr spcFirstLastPara="0" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
           <a:noAutofit/>
         </a:bodyPr>
-        <a:lstStyle/>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
         <a:p>
           <a:pPr marL="0" indent="0" algn="l"/>
           <a:r>
@@ -171,7 +266,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>MajorsGetViewController</a:t>
+            <a:t>LoginViewController</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -181,25 +276,25 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>438150</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="四角形 5">
+        <xdr:cNvPr id="3" name="四角形 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F65AAC4-BD9B-4FE1-A19D-E8B9713BF231}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5B8EF61-9ED3-4EBE-8FE1-243E19603C4B}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{822B201D-DF36-4DB1-A2CC-BF7C2A34D922}"/>
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{A92F80CA-9A40-43A6-AC20-AAAD467F4BB0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -207,7 +302,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1123950" y="3848100"/>
+          <a:off x="1085850" y="3028950"/>
           <a:ext cx="9020175" cy="876300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -344,7 +439,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>@GetMapping("/manager/majors_view")</a:t>
+            <a:t>@GetMapping("/manager/login")</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -356,7 +451,378 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>majorsView ( session : HttpSession, model : Model)</a:t>
+            <a:t>loginView( session : HttpSession, model : Model )</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{014E8138-6AE1-4DCC-9697-A11F5344202F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="695325" y="1066800"/>
+          <a:ext cx="12677775" cy="6562725"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>SubjectGetViewController</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B831C2DD-F34F-4EFD-BB87-10FE70C463D5}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{014E8138-6AE1-4DCC-9697-A11F5344202F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1085850" y="3600450"/>
+          <a:ext cx="9020175" cy="1028700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>@GetMapping("/manager/subject_view")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>subjectView( session : HttpSession, model : Model )</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1007,7 +1473,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>formView( session : HttpSession, model : Model, id : @RequestParam int )</a:t>
+            <a:t>formView( session : HttpSession, model : Model )</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1030,6 +1496,286 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{822B201D-DF36-4DB1-A2CC-BF7C2A34D922}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="1028700"/>
+          <a:ext cx="12677775" cy="5495925"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>MajorsGetViewController</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F65AAC4-BD9B-4FE1-A19D-E8B9713BF231}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{822B201D-DF36-4DB1-A2CC-BF7C2A34D922}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1123950" y="3848100"/>
+          <a:ext cx="9020175" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>@GetMapping("/manager/majors_view")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>majorsView ( session : HttpSession, model : Model)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -1379,377 +2125,6 @@
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t>majorsView( session : HttpSession, model : Model )</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>-r String</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="角丸四角形 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A92F80CA-9A40-43A6-AC20-AAAD467F4BB0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="695325" y="914400"/>
-          <a:ext cx="12677775" cy="5495925"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg2">
-            <a:lumMod val="90000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr spcFirstLastPara="0" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle>
-          <a:lvl1pPr marL="0" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>LoginViewController</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>400050</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="四角形 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5B8EF61-9ED3-4EBE-8FE1-243E19603C4B}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{A92F80CA-9A40-43A6-AC20-AAAD467F4BB0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1085850" y="3028950"/>
-          <a:ext cx="9020175" cy="876300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
-          <a:prstTxWarp prst="textNoShape">
-            <a:avLst/>
-          </a:prstTxWarp>
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle>
-          <a:lvl1pPr marL="0" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>@GetMapping("/manager/login")</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>loginView( session : HttpSession, model : Model )</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2120,7 +2495,938 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>majorView( session : HttpSession, model : Model, id : @RequestParam int )</a:t>
+            <a:t>majorView( session : HttpSession, model : Model )</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFB4C403-0C57-4B56-A984-2B77358860D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="1219200"/>
+          <a:ext cx="12677775" cy="6524625"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>SubjectRegisterViewController</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2F2718A-EFE1-4F75-97AA-6A9B2BAB1653}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{DFB4C403-0C57-4B56-A984-2B77358860D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1076325" y="2895600"/>
+          <a:ext cx="9020175" cy="1028700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>@GetMapping("/manager/subject_register")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>formView( session : HttpSession, model Model)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84CC991B-BBB4-43AF-8043-1C774A96C29D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="695325" y="1066800"/>
+          <a:ext cx="12677775" cy="6562725"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>SubjectSetViewController</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{571AADA4-050F-483A-AF3B-A8E69AA01485}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{84CC991B-BBB4-43AF-8043-1C774A96C29D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1085850" y="3286125"/>
+          <a:ext cx="9020175" cy="1066800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>@GetMapping("/manager/subject_update_view")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>formView( session : HttpSession, model : Model )</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA6A1DCC-0715-4A73-B073-E99C6788A56C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="1219200"/>
+          <a:ext cx="12677775" cy="6524625"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>SubjectsGetViewController</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7CBC37B-75E7-4859-8BCC-9B8786173BA0}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{EA6A1DCC-0715-4A73-B073-E99C6788A56C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1123950" y="4572000"/>
+          <a:ext cx="9020175" cy="1028700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>@GetMapping("/manager/subjects_view")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>subjectsView ( session : HttpSession, model : Model)</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2458,21 +3764,43 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FAD6FA3-7B26-471B-B3D8-8BC601EF4900}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A4375CD-953A-4466-B799-B5CFC9858533}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B84D7B29-3C9C-44D3-8A6B-82ABF7D31D32}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEC717DF-E762-4C42-8B2A-13EBBCCB06FD}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63A8633E-387F-40CD-BD90-4057C77280B7}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2483,7 +3811,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8829FDBE-9BFC-4C0E-89F2-C13862F39AFB}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2492,20 +3820,21 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA2B0658-91AA-4EFF-842D-3941C1AF5682}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FAD6FA3-7B26-471B-B3D8-8BC601EF4900}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A4375CD-953A-4466-B799-B5CFC9858533}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA2B0658-91AA-4EFF-842D-3941C1AF5682}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2516,7 +3845,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23901DE6-5F7D-4F8C-96AD-8F2E5E915077}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2527,9 +3856,31 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B570C0A3-9704-4150-B1EB-E56BF2A1A796}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC3143E7-A27C-411C-9B87-C8DD6C19E8D6}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC3C362B-0642-4129-9EA8-A7BF6F1171C5}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/class_diagram/controller/view/manager/成績管理sys_クラス図_controller_view_manager.xlsx
+++ b/class_diagram/controller/view/manager/成績管理sys_クラス図_controller_view_manager.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\java_fri_sys\seiseki_manage_sys\class_diagram\controller\view\manager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{C8350AB1-25A6-4527-B69B-A86CB26EC45D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFAC53B5-5635-4683-9743-7DBC6A9E978D}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="13_ncr:1_{C8350AB1-25A6-4527-B69B-A86CB26EC45D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D6B1D8B-ECB7-41D5-A1E9-B41E66A23DE0}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="9" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginViewController" sheetId="8" r:id="rId1"/>
@@ -24,6 +24,10 @@
     <sheet name="SubjectSetViewController" sheetId="10" r:id="rId9"/>
     <sheet name="SubjectsGetViewController" sheetId="12" r:id="rId10"/>
     <sheet name="SubjectGetViewController" sheetId="9" r:id="rId11"/>
+    <sheet name="ClassGetViewController" sheetId="13" r:id="rId12"/>
+    <sheet name="ClassesGetViewController" sheetId="14" r:id="rId13"/>
+    <sheet name="ClassSetViewController" sheetId="15" r:id="rId14"/>
+    <sheet name="ClassRegisterViewController" sheetId="16" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -823,6 +827,1308 @@
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t>subjectView( session : HttpSession, model : Model )</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8CBB3D8-B564-4213-9030-F2DED1C3E097}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="695325" y="914400"/>
+          <a:ext cx="12677775" cy="5495925"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>ClassGetViewController</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FF921D3-BDB8-48CD-8E9F-C1B221DE258B}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{C8CBB3D8-B564-4213-9030-F2DED1C3E097}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1085850" y="3028950"/>
+          <a:ext cx="9020175" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>@GetMapping("/manager/class_view")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>classView( session : HttpSession, model : Model )</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C411D5F6-E461-464A-858F-5FE986F57A2C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="1028700"/>
+          <a:ext cx="12677775" cy="5495925"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>ClassesGetViewController</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{655203BF-6E18-49DF-899D-3B17DC089D3E}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{C411D5F6-E461-464A-858F-5FE986F57A2C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1123950" y="3848100"/>
+          <a:ext cx="9020175" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>@GetMapping("/manager/classes_view")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>classesView ( session : HttpSession, model : Model)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE47B93A-D729-45E9-B416-E4FA769C05A2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="695325" y="914400"/>
+          <a:ext cx="12677775" cy="5495925"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>ClassSetViewController</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC8FC827-B351-419D-A1C1-8A3D5D685983}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{EE47B93A-D729-45E9-B416-E4FA769C05A2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1085850" y="2790825"/>
+          <a:ext cx="9020175" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>@GetMapping("/manager/class_update_view")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>formView( session : HttpSession, model : Model )</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4ACFB1BA-D73F-4A38-B9B1-6C98BAE58886}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="1028700"/>
+          <a:ext cx="12677775" cy="5495925"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>ClassRegisterViewController</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8E53F68-BF3C-466C-BBD3-BD1B3BBB22D0}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{4ACFB1BA-D73F-4A38-B9B1-6C98BAE58886}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1076325" y="2438400"/>
+          <a:ext cx="9020175" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>@GetMapping("/manager/class_register")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>formView( session : HttpSession, model Model)</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -3797,6 +5103,51 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89F2D685-0A59-4CAF-B9E4-3F2AD7AA86B2}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31552B8C-B0A8-4A6B-9F59-83F43E2F3EC1}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{802CD9B3-253D-445B-A374-F1D2992B8649}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51877DE4-4433-45E0-AD96-273147CA9CA8}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63A8633E-387F-40CD-BD90-4057C77280B7}">
   <dimension ref="A1"/>

--- a/class_diagram/controller/view/manager/成績管理sys_クラス図_controller_view_manager.xlsx
+++ b/class_diagram/controller/view/manager/成績管理sys_クラス図_controller_view_manager.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29704"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\java_fri_sys\seiseki_manage_sys\class_diagram\controller\view\manager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="13_ncr:1_{C8350AB1-25A6-4527-B69B-A86CB26EC45D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D6B1D8B-ECB7-41D5-A1E9-B41E66A23DE0}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="13_ncr:1_{C8350AB1-25A6-4527-B69B-A86CB26EC45D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F933FF36-A087-4A8A-9582-414A5B30EB61}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="9" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="14" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginViewController" sheetId="8" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <sheet name="ClassesGetViewController" sheetId="14" r:id="rId13"/>
     <sheet name="ClassSetViewController" sheetId="15" r:id="rId14"/>
     <sheet name="ClassRegisterViewController" sheetId="16" r:id="rId15"/>
+    <sheet name="ManagerGetViewController" sheetId="17" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -2129,6 +2130,377 @@
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t>formView( session : HttpSession, model Model)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D3E50C0-A1B7-4CCC-A3EE-E3AA59CECEEA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="695325" y="914400"/>
+          <a:ext cx="12677775" cy="5495925"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>ManagerGetViewController</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11500380-2C5A-4942-B0CC-3CF9AB622289}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{6D3E50C0-A1B7-4CCC-A3EE-E3AA59CECEEA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1085850" y="3028950"/>
+          <a:ext cx="9020175" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>@GetMapping("/manager/manager_view")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>managerView( session : HttpSession, model : Model )</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -5148,6 +5520,17 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC754C5-7599-4247-91B3-492E6581E38C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63A8633E-387F-40CD-BD90-4057C77280B7}">
   <dimension ref="A1"/>

--- a/class_diagram/controller/view/manager/成績管理sys_クラス図_controller_view_manager.xlsx
+++ b/class_diagram/controller/view/manager/成績管理sys_クラス図_controller_view_manager.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29704"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\java_fri_sys\seiseki_manage_sys\class_diagram\controller\view\manager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="13_ncr:1_{C8350AB1-25A6-4527-B69B-A86CB26EC45D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F933FF36-A087-4A8A-9582-414A5B30EB61}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="13_ncr:1_{C8350AB1-25A6-4527-B69B-A86CB26EC45D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2AFC626-B280-4A5E-B96A-BD03824C4A07}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="14" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="15" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginViewController" sheetId="8" r:id="rId1"/>
@@ -1955,14 +1955,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>390525</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1980,7 +1980,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1076325" y="2438400"/>
+          <a:off x="1076325" y="2981325"/>
           <a:ext cx="9020175" cy="876300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2142,6 +2142,346 @@
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t>-r String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="四角形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E868B638-E62F-46F8-97A6-3C455149E470}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{F8E53F68-BF3C-466C-BBD3-BD1B3BBB22D0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1066800" y="1914525"/>
+          <a:ext cx="2914650" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>majorService : MajorService</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="四角形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE57E7AB-964E-48E7-912F-D686AC532F7C}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{E868B638-E62F-46F8-97A6-3C455149E470}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4219575" y="1914525"/>
+          <a:ext cx="2914650" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>subjectService : SubjectService</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
